--- a/tests/fixtures/agent3_comparaison_rag.xlsx
+++ b/tests/fixtures/agent3_comparaison_rag.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Absence des compétences sur les outils et frameworks avancés requis comme TensorFlow, PyTorch et Docker.</t>
+          <t>Absence des compétences sur les frameworks de Deep Learning demandés (TensorFlow, PyTorch)</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Manque de certaines compétences transversales demandées telles que l'autonomie, la résolution de problèmes et la gestion de projet.</t>
+          <t>Manque de maîtrise de l'outil de conteneurisation Docker</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>L'expérience de 3 ans du candidat est inférieure aux 5 ans d'expérience minimum requis par l'offre.</t>
+          <t>Compétences transversales manquantes : Autonomie, Résolution de problèmes et Gestion de projet</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>7.17</v>
+        <v>9.31</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>7.17</v>
+        <v>6.03</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="E18" s="9" t="n"/>
     </row>
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>7.83</v>
+        <v>9.94</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>7.17</v>
+        <v>6.03</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.66</v>
+        <v>3.91</v>
       </c>
       <c r="E19" s="9" t="n"/>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Comment concevez-vous l'entraînement d'un modèle de Deep Learning avec PyTorch ou TensorFlow pour un cas d'usage de classification ?</t>
+          <t>Bien que votre parcours se soit concentré sur scikit-learn, comment aborderiez-vous la transition vers PyTorch ou TensorFlow pour concevoir un réseau de neurones profond ?</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -750,12 +750,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>PyTorch / TensorFlow</t>
+          <t>TensorFlow / PyTorch</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Cible l'écart identifié sur l'absence de compétences avec les frameworks PyTorch et TensorFlow requis par l'offre.</t>
+          <t>Évalue la capacité à s'adapter aux frameworks de Deep Learning demandés dans l'offre.</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Quelle méthode utilisez-vous pour conteneuriser une application Python de Machine Learning à l'aide de Docker afin de préparer sa mise en production ?</t>
+          <t>Dans le cadre de la mise en production de vos modèles, comment rédigeriez-vous un fichier Dockerfile optimisé pour une application Python de Machine Learning ?</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Cible l'écart sur l'absence de maîtrise de l'outil Docker demandée dans l'offre.</t>
+          <t>Permet de vérifier la maîtrise de la conteneurisation Docker mentionnée dans les prérequis de l'offre.</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Racontez une situation où vous avez fait face à un problème technique bloquant sans avoir de référent technique disponible pour vous aider. Comment avez-vous résolu ce problème en autonomie ?</t>
+          <t>Racontez une situation lors de vos expériences chez DataVision où vous avez dû mener à bien une analyse de données ou un modèle sans encadrement direct.</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Autonomie et résolution de problèmes</t>
+          <t>Autonomie</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Cible le manque de compétences transversales en autonomie et résolution de problèmes souligné dans l'évaluation.</t>
+          <t>Permet d'évaluer la compétence transversale d'autonomie recherchée par l'entreprise Novatech AI.</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Si vous devez planifier et coordonner la mise en place d'un pipeline de données avec plusieurs parties prenantes, comment gérez-vous les priorités du projet ?</t>
+          <t>Face à un modèle de Machine Learning développé avec scikit-learn dont les performances se dégradent subitement sur des données de production, quelle démarche méthodique adoptez-vous pour identifier la source du problème ?</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -825,12 +825,12 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Gestion de projet</t>
+          <t>Résolution de problèmes</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Cible l'écart d'évaluation concernant la compétence transversale de gestion de projet requise pour le poste.</t>
+          <t>Cible la capacité de résolution de problèmes face à un dysfonctionnement technique en production.</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>L'offre exige un minimum de cinq ans d'expérience alors que vous en avez trois. Face à une décision d'architecture complexe pour laquelle vous manquez de recul, quelle est votre stratégie pour sécuriser votre choix ?</t>
+          <t>Vous devez livrer un pipeline de traitement de données et un modèle prédictif dans un délai serré tout en jonglant avec des demandes de modification de dernière minute. Comment priorisez-vous vos tâches ?</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Expérience et montée en compétences</t>
+          <t>Gestion de projet</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Cible directement l'écart de durée d'expérience entre le profil du candidat (3 ans) et les exigences de l'offre (5 ans minimum).</t>
+          <t>Évalue la compétence en gestion de projet et la capacité à gérer les priorités dans un contexte opérationnel.</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Lors de l'optimisation des hyperparamètres d'un modèle avec scikit-learn, comment procédez-vous pour éviter le surapprentissage sur un jeu de données limité ?</t>
+          <t>Dans votre expérience chez DataVision, quels types de validateurs croisés avez-vous privilégiés avec scikit-learn pour évaluer vos modèles prédictifs ?</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>S'appuie sur la maîtrise déclarée de scikit-learn et l'expérience en Machine Learning du CV de la candidate.</t>
+          <t>Valide la maîtrise déclarée de scikit-learn et des pratiques d'évaluation de modèles.</t>
         </is>
       </c>
     </row>
@@ -890,22 +890,22 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Comment adaptez-vous votre discours lorsque vous devez présenter les résultats d'une analyse de données à des décideurs ou des équipes métiers non techniques ?</t>
+          <t>Comment optimisez-vous une requête SQL complexe manipulant de grands volumes de données dans le cadre de la préparation de vos jeux d'entraînement ?</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>comportementale</t>
+          <t>technique</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>S'appuie sur la compétence transversale de communication mentionnée dans le profil et attendue par l'offre.</t>
+          <t>Fait le lien entre l'expérience de la candidate sur l'analyse de données SQL et les besoins de développement de pipelines de données de l'offre.</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Comment comptez-vous monter en compétence sur des frameworks de Deep Learning comme TensorFlow ou PyTorch, sachant que votre expérience actuelle repose principalement sur scikit-learn ?</t>
+          <t>Bien que votre parcours mentionne scikit-learn, comment envisagez-vous votre apprentissage et votre utilisation de frameworks de Deep Learning tels que TensorFlow ou PyTorch pour ce poste ?</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Cible l'écart identifié concernant l'absence de compétences sur les frameworks avancés requis par l'offre.</t>
+          <t>Permet d'évaluer la capacité du candidat à combler l'écart sur les frameworks de Deep Learning requis par l'offre.</t>
         </is>
       </c>
     </row>
@@ -974,22 +974,22 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Pouvez-vous décrire une situation où vous avez dû gérer un projet d'analyse de données de bout en bout en totale autonomie ?</t>
+          <t>Comment appréhendez-vous l'utilisation de Docker pour la conteneurisation et le déploiement de modèles de Machine Learning dans un environnement de production ?</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>comportementale</t>
+          <t>technique</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Autonomie et gestion de projet</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Cible le manque de compétences transversales demandées telles que l'autonomie et la gestion de projet.</t>
+          <t>Cible directement le manque de maîtrise de l'outil de conteneurisation identifié dans le profil du candidat.</t>
         </is>
       </c>
     </row>
@@ -999,22 +999,22 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>L'offre requiert 5 ans d'expérience minimum, tandis que votre parcours totalise environ 3 ans. Comment pensez-vous combler cet écart pour assumer rapidement les responsabilités attendues ?</t>
+          <t>Pourriez-vous partager un exemple concret issu de votre expérience chez DataVision où vous avez dû faire preuve d'une grande autonomie pour mener à bien une tâche d'analyse ?</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>situationnelle</t>
+          <t>comportementale</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Expérience professionnelle</t>
+          <t>Autonomie</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Cible directement l'écart entre l'expérience du candidat et les 5 ans minimum requis par l'offre.</t>
+          <t>Évalue la compétence transversale d'autonomie mentionnée comme manquante par rapport aux attentes de l'offre.</t>
         </is>
       </c>
     </row>
@@ -1024,22 +1024,22 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Quels critères utilisez-vous pour évaluer la performance d'un modèle de classification développé avec scikit-learn ?</t>
+          <t>Face à un modèle de Machine Learning dont les performances de prédiction stagnent ou se dégradent, quelle méthodologie suivez-vous pour identifier et résoudre ce type de problème ?</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>technique</t>
+          <t>situationnelle</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>scikit-learn</t>
+          <t>Résolution de problèmes</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>S'appuie sur l'expérience concrète de la candidate avec scikit-learn mentionnée dans son CV.</t>
+          <t>Permet de tester la compétence de résolution de problèmes dans un contexte technique proche du poste.</t>
         </is>
       </c>
     </row>
@@ -1049,22 +1049,22 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Comment procédez-vous pour optimiser une requête SQL complexe lors de la phase de préparation de données ?</t>
+          <t>Comment gérez-vous l'organisation, le suivi des livrables et la priorisation des tâches lors de la réalisation d'un projet de data science de bout en bout ?</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>technique</t>
+          <t>comportementale</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>Gestion de projet</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>S'appuie sur la maîtrise de SQL mentionnée dans le profil et requise pour l'analyse de données.</t>
+          <t>Aborde l'écart identifié concernant la gestion de projet en s'appuyant sur l'organisation professionnelle du candidat.</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Comment vous y prenez-vous pour communiquer les résultats techniques d'un modèle de Machine Learning à des équipes métiers ?</t>
+          <t>Quels critères d'évaluation de performance privilégiez-vous lors du développement de modèles supervisés avec scikit-learn dans vos projets précédents ?</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>comportementale</t>
+          <t>technique</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>scikit-learn</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Valorise la compétence en communication du profil tout en répondant aux besoins de collaboration de l'offre.</t>
+          <t>Valorise un point fort du profil tout en évaluant techniquement la rigueur méthodologique du candidat.</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Avez-vous déjà manipulé des conteneurs pour isoler des environnements de développement ou de test ?</t>
+          <t>De quelle manière procédez-vous pour structurer et optimiser vos requêtes SQL lors de l'extraction de données complexes pour une analyse exploratoire ?</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Aborde l'outil Docker requis dans l'offre et absent du profil.</t>
+          <t>S'appuie sur l'expérience concrète en SQL mentionnée dans le CV pour évaluer la maîtrise pratique de l'outil.</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Absence des compétences techniques suivantes : Python, Machine Learning, scikit-learn, TensorFlow, PyTorch, Docker, Git et développement de pipelines de données</t>
+          <t>Absence de compétences techniques clés en IA/ML : Python, Machine Learning, scikit-learn, TensorFlow, PyTorch</t>
         </is>
       </c>
     </row>
@@ -1234,68 +1234,63 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Absence des compétences comportementales requises : Autonomie et Résolution de problèmes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+          <t>Absence d'outils et pratiques : Docker, Git, développement de pipelines de données</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Manque de certaines compétences transversales requises : autonomie et résolution de problèmes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>2. SYNTHESE COMPARATIVE (VOLUME / TEMPS DE REPONSE)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Metrique</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Avec RAG</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Sans RAG</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Ecart</t>
         </is>
       </c>
-      <c r="E13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Nombre de questions generees</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="C14" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="9" t="n"/>
+      <c r="E14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Nombre de questions demandees</t>
+          <t>Nombre de questions generees</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>0</v>
@@ -1305,124 +1300,116 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Temps retrieval FAISS (s)</t>
+          <t>Nombre de questions demandees</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="E16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Temps generation Gemini (s)</t>
+          <t>Temps retrieval FAISS (s)</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>0.01</v>
+        <v>0.26</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="E17" s="9" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
+          <t>Temps generation Gemini (s)</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
           <t>Temps total (s)</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E18" s="9" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="B19" s="9" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="E19" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>3. QUESTIONS GENEREES — AVEC RAG</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Competence ciblee</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>Justification</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Etant donné votre solide expérience en SQL et Business Intelligence, comment comptez-vous aborder la transition vers le langage Python pour concevoir vos premiers scripts de manipulation de données ?</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>technique</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>Le candidat maîtrise le SQL mais l'offre exige Python, ce qui constitue un écart identifié.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Dans le cadre de l'utilisation de bibliothèques comme scikit-learn ou TensorFlow, comment envisagez-vous l'évaluation des performances d'un modèle prédictif par rapport aux indicateurs de reporting que vous suivez habituellement en BI ?</t>
+          <t>Lors de l'évaluation d'un modèle de classification avec scikit-learn, comment gérez-vous le déséquilibre des classes pour éviter un taux de faux négatifs élevé ?</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1432,22 +1419,22 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>scikit-learn</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Permet d'évaluer la transition du candidat vers le Machine Learning et l'utilisation de scikit-learn/TensorFlow/PyTorch.</t>
+          <t>L'offre exige la maîtrise de scikit-learn et du Machine Learning, un écart identifié par rapport à son profil orienté BI.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Comment concevez-vous l'intégration et le déploiement d'un pipeline de traitement de données conteneurisé avec Docker au sein d'un flux de travail Git ?</t>
+          <t>Dans le cadre de l'utilisation de frameworks de Deep Learning comme PyTorch ou TensorFlow, comment concevez-vous l'architecture d'un réseau de neurones simple pour traiter des données tabulaires ?</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1457,181 +1444,181 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Docker et Git</t>
+          <t>TensorFlow / PyTorch</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>L'offre exige des compétences sur Docker, Git et les pipelines de données qui ne figurent pas dans le profil du candidat.</t>
+          <t>L'offre requiert des compétences en TensorFlow et PyTorch, absentes de son parcours actuel.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>En tant que manager et senior habitué à travailler en équipe, pouvez-vous nous décrire une situation où vous avez dû mener à bien un projet complexe en totale autonomie ?</t>
+          <t>Comment utilisez-vous Docker pour garantir la reproductibilité d'un environnement d'entraînement de modèle entre votre poste de développement et la production ?</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>comportementale</t>
+          <t>technique</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Autonomie</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>L'écart identifié pointe le besoin d'évaluer l'autonomie du candidat face à des environnements techniques nouveaux.</t>
+          <t>L'utilisation de Docker fait partie des outils requis par l'offre mais non mentionnés dans le CV.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Face à un modèle de Machine Learning en production dont la précision chute subitement, quelle démarche méthodique suivez-vous pour identifier la source du problème et le corriger ?</t>
+          <t>Dans le cadre du développement de pipelines de données, comment structurez-vous vos branches sur Git pour collaborer efficacement sur le code d'ingestion et les scripts de modélisation ?</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>situationnelle</t>
+          <t>technique</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Résolution de problèmes</t>
+          <t>Git et pipelines de données</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Cible directement la compétence comportementale de résolution de problèmes requise pour le poste.</t>
+          <t>L'offre demande le développement de pipelines de données et l'usage de Git, compétences absentes de son CV.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Vous devez concevoir un prototype de Machine Learning sur un nouveau jeu de données sans spécifications claires et en totale autonomie. Quelle méthodologie de résolution de problèmes suivez-vous pour cadrer le besoin initial ?</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>situationnelle</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Autonomie et résolution de problèmes</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>L'autonomie et la résolution de problèmes sont des compétences transversales explicitement requises par l'offre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Comment exploitez-vous votre expertise en SQL et en structuration de bases de données pour optimiser la phase de préparation des données en amont des projets analytiques ?</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>technique</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Traitement et analyse de données</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>Valorise l'expérience forte du candidat tout en vérifiant sa capacité à répondre aux exigences de préparation de données de l'offre.</t>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Racontez une situation où vous avez dû collaborer étroitement avec des profils techniques et des équipes métiers pour aligner un projet orienté data sur les objectifs de l'entreprise.</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>comportementale</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Travail en équipe et communication</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>L'offre exige une forte collaboration avec les équipes techniques et métiers, faisant écho à son expérience de management.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Comment exploitez-vous vos compétences avancées en SQL pour préparer, nettoyer et analyser de gros volumes de données en amont d'un projet analytique ?</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>technique</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>SQL / traitement et analyse de données</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Le candidat possède une solide expérience en SQL, une compétence technique partagée entre son profil BI et l'offre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>4. QUESTIONS GENEREES — SANS RAG</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>Competence ciblee</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>Justification</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>Comment envisagez-vous la transition de vos compétences en SQL et Power BI vers l'utilisation de Python pour le Machine Learning ?</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>technique</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Python et Machine Learning</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>Évalue la capacité à transposer l'expérience analytique vers Python et les algorithmes de ML.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>Quels sont vos apprentissages ou expériences avec des bibliothèques comme scikit-learn, TensorFlow ou PyTorch ?</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>technique</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>scikit-learn, TensorFlow et PyTorch</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>Aborde l'absence de ces bibliothèques majeures requises pour le poste.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Comment concevez-vous le développement d'un pipeline de données robuste intégrant Docker et Git pour le versioning ?</t>
+          <t>Comment envisagez-vous la transition de vos compétences en analyse de données vers le développement de modèles prédictifs en Python en utilisant la bibliothèque scikit-learn ?</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -1641,103 +1628,179 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Pipelines de données, Docker et Git</t>
+          <t>Python et Machine Learning</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Cible directement l'écart sur le déploiement et l'ingénierie des données.</t>
+          <t>Permet d'évaluer la capacité du candidat à combler l'écart sur Python et le Machine Learning à partir de son bagage analytique.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Pouvez-vous nous donner un exemple où vous avez dû faire preuve d'une grande autonomie pour mener à bien un projet complexe ?</t>
+          <t>Avez-vous déjà eu l'occasion d'étudier ou d'utiliser des frameworks de Deep Learning tels que TensorFlow ou PyTorch dans le cadre de vos projets ou formations passées ?</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>comportementale</t>
+          <t>technique</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Autonomie</t>
+          <t>TensorFlow / PyTorch</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Évalue la compétence comportementale d'autonomie requise dans l'offre.</t>
+          <t>Cible directement le manque de compétences sur ces bibliothèques spécifiques requises dans l'offre.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Décrivez une situation professionnelle où vous avez fait face à un problème complexe nécessitant une résolution rapide et innovante.</t>
+          <t>Quel est votre niveau de familiarité avec l'outil Docker pour la conteneurisation et le déploiement d'applications ou de modèles ?</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>comportementale</t>
+          <t>technique</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Résolution de problèmes</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Permet de vérifier la capacité de résolution de problèmes face à des défis inattendus.</t>
+          <t>Evalue l'écart identifié concernant l'absence de maîtrise de l'outil Docker.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Comment procédez-vous pour concevoir et versionner des pipelines de traitement de données en utilisant Git pour assurer la traçabilité du code ?</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>technique</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Git et pipelines de données</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Cible l'écart sur les pratiques de développement (Git) et la construction de pipelines de données.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Face à un problème technique bloquant et inédit pour lequel vous n'avez pas de solution immédiate, quelle démarche autonome suivez-vous pour le résoudre ?</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>situationnelle</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Autonomie et résolution de problèmes</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Evalue la compétence transversale d'autonomie et de résolution de problèmes identifiée comme un écart par rapport aux attentes de l'offre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Face à un modèle de Machine Learning dont les performances en production se dégradent, quelle démarche méthodologique adoptez-vous ?</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>situationnelle</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>Maintenance et évaluation de modèles</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>Teste la réaction face à un scénario critique typique d'un poste de ML Engineer.</t>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>En vous appuyant sur votre longue expérience avec SQL, comment structurez-vous l'extraction de données complexes pour préparer l'alimentation d'un modèle ?</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>technique</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>SQL et traitement de données</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Valorise l'expertise solide du candidat en SQL tout en l'orientant vers la préparation de données demandée par l'offre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Décrivez une situation où vous avez dû collaborer étroitement avec des équipes techniques aux profils différents des vôtres pour mener à bien un projet analytique.</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>comportementale</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Travail en équipe et communication</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Permet d'évaluer les compétences relationnelles et de collaboration inter-équipes mentionnées dans l'offre.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
+    <mergeCell ref="A21:E21"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A20:E20"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B11:E11"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="B10:E10"/>
+    <mergeCell ref="A31:E31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1828,7 +1891,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Absence des compétences en Machine Learning et des bibliothèques associées telles que scikit-learn, TensorFlow et PyTorch.</t>
+          <t>Absence de compétences en Machine Learning, scikit-learn, TensorFlow et PyTorch.</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1903,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Manque de maîtrise des outils de conteneurisation et de versioning comme Docker et Git.</t>
+          <t>Compétences techniques manquantes : Docker et Git.</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1915,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>La compétence en gestion de projet n'est pas identifiée dans le profil.</t>
+          <t>Compétence transversale manquante : Gestion de projet.</t>
         </is>
       </c>
     </row>
@@ -1948,13 +2011,13 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>6.7</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>6.35</v>
+        <v>6.04</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.35</v>
+        <v>2.08</v>
       </c>
       <c r="E18" s="9" t="n"/>
     </row>
@@ -1965,13 +2028,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>7</v>
+        <v>8.42</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>6.35</v>
+        <v>6.04</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.65</v>
+        <v>2.38</v>
       </c>
       <c r="E19" s="9" t="n"/>
     </row>
@@ -2015,7 +2078,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Comment appréhendez-vous la transition de l'analyse statistique descriptive vers le Machine Learning prédictif avec scikit-learn pour éviter le surapprentissage sur de nouvelles données ?</t>
+          <t>Comment utiliseriez-vous scikit-learn pour mettre en place un pipeline de classification supervisée tout en évitant le data leakage lors de la validation croisée ?</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -2025,12 +2088,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>scikit-learn</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Cible directement l'écart identifié concernant l'absence de compétences en Machine Learning et l'utilisation de scikit-learn.</t>
+          <t>Cible l'écart identifié sur le Machine Learning et scikit-learn requis par l'offre, tout en s'appuyant sur le background en modélisation statistique du profil.</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2103,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>N'ayant pas d'expérience directe avec Docker mentionnée dans votre profil, comment mettriez-vous en œuvre la conteneurisation d'un script Python de traitement de données pour garantir sa reproductibilité ?</t>
+          <t>Comment structurez-vous un Dockerfile pour une application Python de traitement de données afin de minimiser la taille de l'image finale et d'optimiser le cache de construction ?</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -2055,7 +2118,7 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Permet d'évaluer la capacité du candidat à combler l'écart sur les outils de conteneurisation requis par l'offre.</t>
+          <t>Cible la compétence technique manquante (Docker) en l'adaptant à l'écosystème Python principal du candidat.</t>
         </is>
       </c>
     </row>
@@ -2065,22 +2128,22 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>En l'absence d'expérience formelle en gestion de projet sur votre CV, comment gérez-vous la priorisation et le suivi des livrables lors d'un projet de modélisation de données soumis à des contraintes de temps ?</t>
+          <t>Un bogue critique est apparu en production entre deux versions distantes de code, mais personne ne sait quelle modification l'a introduit. Comment utilisez-vous git bisect pour isoler le commit responsable ?</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>situationnelle</t>
+          <t>technique</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Gestion de projet</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Cible explicitement l'écart sur la gestion de projet tout en s'appuyant sur l'expérience en modélisation de données du candidat.</t>
+          <t>Cible la compétence technique manquante (Git) en reprenant une approche similaire issue de la base de questions.</t>
         </is>
       </c>
     </row>
@@ -2090,22 +2153,22 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>L'offre requiert des compétences sur TensorFlow ou PyTorch. Face à ce manque dans votre parcours actuel, quelle démarche d'auto-formation mettriez-vous en place pour concevoir un premier réseau de neurones ?</t>
+          <t>Lors d'un projet d'analyse ou de modélisation, l'équipe sous-estime régulièrement la complexité des tâches, ce qui entraîne des retards sur les livrables. Quelle stratégie mettez-vous en place pour réajuster le suivi et respecter les engagements ?</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>comportementale</t>
+          <t>situationnelle</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TensorFlow / PyTorch</t>
+          <t>Gestion de projet</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Évalue l'autonomie et la capacité d'apprentissage rapide du candidat face à un écart technique majeur identifié.</t>
+          <t>Cible directement l'écart sur la compétence transversale manquante (Gestion de projet) en lien avec les livrables du poste.</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2178,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Comment organisez-vous votre workflow avec Git lors d'un travail collaboratif sur un code source pour éviter les conflits de fusion majeurs lors des livraisons ?</t>
+          <t>Dans quel cas d'usage privilégiez-vous la création d'un générateur personnalisé avec yield plutôt qu'une liste en compréhension lors de la manipulation de gros fichiers de données en Python ?</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -2125,12 +2188,12 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Cule l'écart concernant le manque de maîtrise des outils de versioning requis pour le poste.</t>
+          <t>S'appuie sur la maîtrise déclarée de Python et Pandas pour évaluer la capacité du candidat à optimiser ses traitements de données.</t>
         </is>
       </c>
     </row>
@@ -2140,22 +2203,22 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Dans le cadre de vos expériences de Data Analyst avec Python, comment optimisez-vous le traitement de grands volumes de données tabulaires avec Pandas pour éviter les saturations mémoire ?</t>
+          <t>Racontez une situation où vous avez dû communiquer des résultats complexes ou des marges d'erreur à des équipes métiers ou des décideurs non techniques.</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>technique</t>
+          <t>comportementale</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Pandas</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>S'appuie sur une compétence forte du CV (Python/Pandas) pour évaluer la maîtrise technique sur le traitement de données.</t>
+          <t>Valorise l'expérience du candidat dans la présentation de résultats tout en répondant aux exigences de communication de l'offre.</t>
         </is>
       </c>
     </row>
@@ -2165,22 +2228,22 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Racontez une situation où vous avez dû présenter des résultats d'analyses complexes à des équipes métiers non techniques pour orienter leurs décisions.</t>
+          <t>Face à un pipeline de données Python existant qui échoue en cours d'exécution sur un gros volume de données, quelle méthode d'analyse utilisez-vous pour diagnostiquer l'origine du problème ?</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>comportementale</t>
+          <t>situationnelle</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>développement de pipelines de données</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Valorise l'expérience du candidat dans la présentation de résultats aux équipes métiers tout en répondant aux compétences transversales de l'offre.</t>
+          <t>Évalue l'aptitude du candidat à concevoir et maintenir des pipelines de données, une exigence majeure de l'offre.</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2287,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Comment envisagez-vous l'utilisation de bibliothèques telles que scikit-learn ou PyTorch pour concevoir des modèles de Machine Learning par rapport à vos compétences actuelles en modélisation statistique ?</t>
+          <t>Comment mettriez-vous en oeuvre un algorithme de classification simple avec scikit-learn pour un nouveau jeu de donnees ?</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -2234,12 +2297,12 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>scikit-learn</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Permet d'évaluer la capacité du candidat à combler l'écart identifié sur l'absence de compétences en Machine Learning et ses bibliothèques associées.</t>
+          <t>Evalue la capacite a apprehender scikit-learn malgre l'absence de cette competence dans le profil.</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2312,7 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Quelle est votre expérience pratique avec l'utilisation de Git pour le versioning de code lors de vos projets de développement en Python ?</t>
+          <t>Quel est l'interet d'utiliser Docker pour conteneuriser une application Python destinee a la production ?</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -2259,12 +2322,12 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Cible directement le manque de maîtrise des outils de versioning identifié dans l'analyse des écarts.</t>
+          <t>Aborde la competence Docker manquante dans le profil pour le poste de Machine Learning Engineer.</t>
         </is>
       </c>
     </row>
@@ -2274,22 +2337,22 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Comment procédez-vous pour planifier et suivre l'avancement des tâches lorsque vous devez mener un projet de données en autonomie de la conception jusqu'à la restitution ?</t>
+          <t>Comment gerez-vous le versioning de code et les conflits de fusion avec Git lors d'un travail en equipe ?</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>situationnelle</t>
+          <t>technique</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Gestion de projet</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>Permet d'évaluer les aptitudes en gestion de projet, compétence non identifiée dans le profil initial du candidat.</t>
+          <t>Permet d'evaluer la maitrise de Git, absente du CV, requise pour la collaboration technique.</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2362,22 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Avez-vous déjà eu l'occasion d'utiliser ou d'interagir avec des conteneurs Docker pour préparer des environnements d'exécution pour vos scripts de traitement de données ?</t>
+          <t>Face a des exigences metier changeantes sur un projet d'analyse de donnees, comment prioriseriez-vous les taches ?</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>technique</t>
+          <t>situationnelle</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>Gestion de projet</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Concerne l'écart identifié sur la maîtrise des outils de conteneurisation requis par l'offre.</t>
+          <t>Cible la competence transversale de gestion de projet absente des experiences explicites.</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2387,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Comment structurez-vous vos scripts Python et l'utilisation de Pandas pour développer des pipelines de traitement de données efficaces et automatisés ?</t>
+          <t>Comment optimisez-vous le traitement d'un grand volume de donnees avec Pandas en Python ?</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -2339,7 +2402,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>S'appuie sur l'expérience en Python et automatisation du candidat pour l'évaluer sur l'exigence de pipelines de données de l'offre.</t>
+          <t>S'appuie sur l'experience Data Analyst de la candidate avec Python et Pandas.</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2412,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Pouvez-vous décrire une situation passée où vous avez dû collaborer étroitement avec des équipes métiers pour expliquer des résultats d'analyses complexes ?</t>
+          <t>Pouvez-vous decrire une situation ou vous avez du presenter des resultats statistiques complexes a des non-specialistes ?</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -2359,12 +2422,12 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Travail en équipe</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Valorise l'expérience du candidat dans la présentation de résultats aux équipes métiers tout en évaluant ses compétences relationnelles.</t>
+          <t>Concerne l'experience de presentation aux equipes metiers mentionnee dans le resume.</t>
         </is>
       </c>
     </row>
@@ -2374,22 +2437,22 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Comment gérez-vous la communication de vos analyses techniques dans un contexte professionnel international nécessitant l'utilisation de l'anglais ?</t>
+          <t>Quelle methode utilisez-vous pour optimiser une requete SQL complexe sur des tables volumineuses ?</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>comportementale</t>
+          <t>technique</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Anglais professionnel</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Fait le lien entre le niveau d'anglais B2 du candidat et l'exigence de l'offre en communication technique et métiers.</t>
+          <t>S'appuie sur l'utilisation de SQL indiquee dans ses experiences chez Market Insights.</t>
         </is>
       </c>
     </row>
